--- a/output/pdf_financials_xlsx/DEFN.xlsx
+++ b/output/pdf_financials_xlsx/DEFN.xlsx
@@ -3607,28 +3607,28 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.3075</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.618726</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.452453</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.621385</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.767862</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.601494</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.56147</v>
       </c>
     </row>
     <row r="93">
@@ -6180,7 +6180,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -7391,7 +7395,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -9463,7 +9471,11 @@
           <t>Reserves 6 4,767,862</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -14733,7 +14745,11 @@
           <t>Reserves 6 307,500</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DEFN.xlsx
+++ b/output/pdf_financials_xlsx/DEFN.xlsx
@@ -814,10 +814,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.116644</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001135</v>
       </c>
     </row>
     <row r="13">
@@ -1362,10 +1362,10 @@
         <v>-4.035213</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.761157</v>
+        <v>-2.877801</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-5.765724</v>
+        <v>-5.766859</v>
       </c>
     </row>
     <row r="28">
@@ -1430,10 +1430,10 @@
         <v>-4.035213</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.761157</v>
+        <v>-2.877801</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.710662</v>
+        <v>-5.711797</v>
       </c>
     </row>
     <row r="30">
@@ -1588,31 +1588,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.236431</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.519823</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.192449</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.166184</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.8494660000000001</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.724812</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.762556</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.916066</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.69526</v>
       </c>
     </row>
     <row r="35">
@@ -1656,31 +1656,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.236431</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.519823</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.192449</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.166184</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.8494660000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.724812</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.762556</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.916066</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.69526</v>
       </c>
     </row>
     <row r="37">
@@ -2064,31 +2064,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.259556</v>
+        <v>0.023125</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.519823</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.256582</v>
+        <v>0.064133</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.199326</v>
+        <v>0.033142</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.160198</v>
+        <v>0.310732</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.769945</v>
+        <v>0.045133</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.856734</v>
+        <v>0.094178</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.046044</v>
+        <v>0.129978</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.750091</v>
+        <v>0.054831</v>
       </c>
     </row>
     <row r="49">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -14288,7 +14288,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -21199,7 +21199,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">

--- a/output/pdf_financials_xlsx/DEFN.xlsx
+++ b/output/pdf_financials_xlsx/DEFN.xlsx
@@ -16404,7 +16404,11 @@
           <t>Broker warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -17362,7 +17366,11 @@
           <t>Broker warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -17907,7 +17915,11 @@
           <t>Broker warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
